--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0186.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0186.xlsx
@@ -16564,7 +16564,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Phù... Suýt nữa thì chết khiếp. Bọn Hoochief có thể đang lao tới chỗ ta đây.</t>
+          <t>Phù... Suýt nữa thì chết khiếp. Bọn Hoochief có thể đang lao tới chỗ tao đây.</t>
         </is>
       </c>
     </row>
@@ -17409,7 +17409,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Gặp khó khăn rồi. Rover đang bối rối.</t>
+          <t>Gặp khó khăn rồi. Vận Mệnh Giả đang bối rối.</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Gặp khó khăn rồi. Rover đang bối rối.</t>
+          <t>Gặp khó khăn rồi. Vận Mệnh Giả đang bối rối.</t>
         </is>
       </c>
     </row>
@@ -17669,7 +17669,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Gặp khó khăn rồi. Rover đang bối rối.</t>
+          <t>Gặp khó khăn rồi. Vận Mệnh Giả đang bối rối.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Gặp khó khăn rồi. Rover đang bối rối.</t>
+          <t>Gặp khó khăn rồi. Vận Mệnh Giả đang bối rối.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Gặp khó khăn rồi. Rover đang bối rối.</t>
+          <t>Gặp khó khăn rồi. Vận Mệnh Giả đang bối rối.</t>
         </is>
       </c>
     </row>
@@ -19489,7 +19489,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Gì? Ta nấu cả đống nấm đấy. Khoan đã...</t>
+          <t>Gì? Tao nấu cả đống nấm đấy. Khoan đã...</t>
         </is>
       </c>
     </row>
@@ -20010,8 +20010,8 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Vấn đề ở đây đã được giải quyết. Nghe nói một Cộng Hưởng Giả mạnh mẽ
-đã giúp đỡ rất nhiều. Thật muốn được gặp {Male=anh ấy;Female=cô ấy} quá.</t>
+          <t>Vấn đề ở đây đã được giải quyết. Nghe nói một Resonator mạnh mẽ
+đã giúp đỡ rất nhiều. Thật muốn được gặp {Male=him;Female=her} quá.</t>
         </is>
       </c>
     </row>
@@ -20531,7 +20531,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Ta nhận nuôi nó vào ngày mười lăm tháng Giêng âm lịch, nên mới đặt tên như vậy. Giống như ta, vì ta sinh ra vào mồng một Tết.</t>
+          <t>Tao nhận nuôi nó vào ngày mười lăm tháng Giêng âm lịch, nên mới đặt tên như vậy. Giống như tao, vì tao sinh ra vào mồng một Tết.</t>
         </is>
       </c>
     </row>
@@ -20791,7 +20791,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Yes.</t>
+          <t>Đúng vậy.</t>
         </is>
       </c>
     </row>
@@ -22741,7 +22741,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Đó là cái hộp thế giới của ta! Chỉ cần ở trong đó, chẳng ai nhìn thấy ta cả! Thế giới sẽ là của ta!</t>
+          <t>Đó là cái hộp thế giới của tao! Chỉ cần ở trong đó, chẳng ai nhìn thấy tao cả! Thế giới sẽ là của tao!</t>
         </is>
       </c>
     </row>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Còn bạn là...?</t>
+          <t>Và ngươi là?</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23716,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Cái, cái hộp này có mấy phần th-thưởng cho cậu đấy! Tạm biệt nhaaa!</t>
+          <t>Cái, cái hộp này có mấy phần th-thưởng cho mày đấy! Tạm biệt nhaaa!</t>
         </is>
       </c>
     </row>
@@ -28201,7 +28201,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Tôi không quan tâm.</t>
+          <t>Tôi không hứng thú.</t>
         </is>
       </c>
     </row>
@@ -28266,7 +28266,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Tính cả ta.</t>
+          <t>Tính cả tao.</t>
         </is>
       </c>
     </row>
@@ -28981,7 +28981,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì vậy?</t>
+          <t>Anh đang làm gì thế?</t>
         </is>
       </c>
     </row>
@@ -31386,7 +31386,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Ta tình cờ nghe lỏm được là khi đi hái những loại cây này… có thể sẽ có những phát hiện bất ngờ đấy.</t>
+          <t>Tao tình cờ nghe lỏm được là khi đi hái những loại cây này… có thể sẽ có những phát hiện bất ngờ đấy.</t>
         </is>
       </c>
     </row>
@@ -31776,7 +31776,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Đừng để lòng tốt của trưởng tộc uổng phí. Dù sao thì cậu cũng là người duy nhất có thể bầu bạn với ta mà.</t>
+          <t>Đừng để lòng tốt của trưởng tộc uổng phí. Dù sao thì cậu cũng là người duy nhất có thể bầu bạn với tao mà.</t>
         </is>
       </c>
     </row>
@@ -32231,7 +32231,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Meow!</t>
+          <t>Meo!</t>
         </is>
       </c>
     </row>
@@ -32296,7 +32296,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Ta muốn làm việc ở nơi gần đầu não Fisalias hơn...</t>
+          <t>Tao muốn làm việc ở nơi gần đầu não Fisalias hơn...</t>
         </is>
       </c>
     </row>
